--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>29.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Azure, GCP, Hadoop, Hive, HBase, Flume</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c843452e183915</t>
+          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=38690ace7c9a024c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
+          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ruby on Rails Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Program Management Solutions</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
+          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Database Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3136af621d112cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Ruby on Rails Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Program Management Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
         </is>
       </c>
     </row>
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
+          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
+          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Institutes for Research</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks / Spark)</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>savantys solutions</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
+          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>American Institutes for Research</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
+          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Senior Data Engineers</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AKUNA CAPITAL</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,129 +1616,129 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lazer</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MuleSoft Consultant</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RADIX INTERNATIONAL CONSULTING</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151dfd13a3d3fb99</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,137 +1791,137 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AKUNA CAPITAL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior SDET II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jaggaer</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,29 +2271,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Developer - DevOps Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52267d9be69a9eef</t>
+          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Developer - DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Jaggaer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50eb133c7651d099</t>
+          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,59 +2516,59 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,15 +2578,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Coloplast</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Architect (Java, AWS, &amp; AI)</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b35823372d99142</t>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, ETL, Power BI, Tableau, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79969044de77605a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tra'Bian Enterprises</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,87 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Tra'Bian Enterprises</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Sr. Engineer, Data - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.9</v>
+        <v>30.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
+          <t>https://www.indeed.com/viewjob?jk=42d62482ae7cddd2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Chinese Mandarin Speaker)</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>29.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38690ace7c9a024c</t>
+          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=38690ace7c9a024c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
+          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ruby on Rails Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Program Management Solutions</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>Ruby on Rails Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Program Management Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
+          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optimus Health Analytics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Optimus Health Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
+          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (AI/ML)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Institutes for Research</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineers</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
+          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>American Institutes for Research</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Senior Data Engineers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AKUNA CAPITAL</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior SDET II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AKUNA CAPITAL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS AI Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SDET II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
+          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jaggaer</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect - GenAI</t>
+          <t>Consultant, Product Architect (P&amp;C Data)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
+          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,137 +2701,137 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Otoe Missouria Group</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tra'Bian Enterprises</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,402 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AWS Devops - AOM</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wexford, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Otoe Missouria Group</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Solutions Architect 4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Edgewater Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tra'Bian Enterprises</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bitus Labs LLC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
+          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>American Institutes for Research</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
+          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Senior Data Engineers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Institutes for Research</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
+          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineers</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
+          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>AKUNA CAPITAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>AWS AI Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior SDET II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AKUNA CAPITAL</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
+          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Visualization Senior Associate - Home Lending Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>Athena, RDS, Scala, Polars, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
+          <t>https://www.indeed.com/viewjob?jk=f4af50f2bafbc222</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS AI Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior SDET II</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant, Product Architect (P&amp;C Data)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Consultant, Product Architect (P&amp;C Data)</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2451,37 +2451,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solution Architect - GenAI</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Cloud Engineer (AWS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Otoe Missouria Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Solutions Architect 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS)</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Otoe Missouria Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
+          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+          <t>https://www.indeed.com/viewjob?jk=162039f0a05caca1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tra'Bian Enterprises</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>Tra'Bian Enterprises</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
         </is>
       </c>
     </row>
@@ -3330,6 +3330,41 @@
         </is>
       </c>
       <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
         </is>

--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
+          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
+          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ruby on Rails Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Program Management Solutions</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
+          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optimus Health Analytics</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Ruby on Rails Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Program Management Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
+          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
+          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>Optimus Health Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
+          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
+          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (AI/ML)</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Java AWS Developer - Face to Face Interview</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Core Alliance Group Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d02124b3f54b0e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AKUNA CAPITAL</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS AI Architect</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
+          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior SDET II</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
+          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Visualization Senior Associate - Home Lending Data &amp; Analytics</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athena, RDS, Scala, Polars, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4af50f2bafbc222</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,112 +2166,112 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS AI Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Consultant, Product Architect (P&amp;C Data)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,147 +2446,147 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ab07eb4acffa0b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b45b6e8aa67df7c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d16dbeaec3930ca</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=90ab5e0fe05ad0e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solution Architect - GenAI</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
+          <t>https://www.indeed.com/viewjob?jk=5c80d6271afc8362</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,137 +2631,137 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=45618c98009db818</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=9716207967dcb05a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>Consultant, Product Architect (P&amp;C Data)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Otoe Missouria Group</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
+          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,94 +3051,94 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162039f0a05caca1</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tra'Bian Enterprises</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,472 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Quality</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Quality</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Quality</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=162039f0a05caca1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>sdq</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Solutions Architect 4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Edgewater Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tra'Bian Enterprises</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Bitus Labs LLC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Senior MuleSoft Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>eBusiness Solutions Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2933456811155d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Atash Enterprises LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=15a88924ef9fe1db</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (AI/ML)</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Institutes for Research</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d02124b3f54b0e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d02124b3f54b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Architect, Software Engineering — Gateway Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, HBase, Kafka, Oracle, PostgreSQL, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
+          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>AWS AI Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
+          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS AI Architect</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,147 +2306,147 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ab07eb4acffa0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b45b6e8aa67df7c</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d16dbeaec3930ca</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Consultant, Product Architect (P&amp;C Data)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ab5e0fe05ad0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c80d6271afc8362</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45618c98009db818</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9716207967dcb05a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Consultant, Product Architect (P&amp;C Data)</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Streamline Defense</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solution Architect - GenAI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,104 +3041,104 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Technical Architect, Integration Development</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>sdq</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect 4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tra'Bian Enterprises</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Power BI, Tableau, Splunk, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162039f0a05caca1</t>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>sdq</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,260 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Tra'Bian Enterprises</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Associate Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Bealls Inc.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Bradenton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Bitus Labs LLC</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
         </is>

--- a/results/job_matches_2026-06-17.xlsx
+++ b/results/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, clustering keys, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,234 +811,234 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
+          <t>https://www.indeed.com/viewjob?jk=82bd622b5093a1e0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ruby on Rails Engineer</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Program Management Solutions</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optimus Health Analytics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25c9deba0321e91</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior MuleSoft Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>eBusiness Solutions Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2933456811155d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Atash Enterprises LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15a88924ef9fe1db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Architect</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eBusiness Solutions Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2933456811155d</t>
+          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atash Enterprises LLC</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a88924ef9fe1db</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
+          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
+          <t>Java AWS Developer - Face to Face Interview</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Core Alliance Group Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
+          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Hadoop, HDFS, Hive, Sqoop, HBase, YARN, Spark</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf338e67f727fc56</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java AWS Developer - Face to Face Interview</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Core Alliance Group Inc.</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,172 +1616,172 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>WesTech Engineering, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>Cloud DevAI Ops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Radiant Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d02124b3f54b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Senior Architect, Software Engineering — Gateway Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, HBase, Kafka, Oracle, PostgreSQL, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>AWS AI Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering — Gateway Platform</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, HBase, Kafka, Oracle, PostgreSQL, Cassandra, NoSQL, Splunk</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS AI Architect</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
+          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df728be8d71a21c</t>
+          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e31041a5ff01e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Tableau Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
+          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Engineer</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Streamline Defense</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Streamline Defense</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Solution Architect - GenAI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Architect - GenAI</t>
+          <t>BSA/AML Modeling Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>FlagStar Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, Power BI, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2127fb9204606d87</t>
+          <t>https://www.indeed.com/viewjob?jk=db3e11992e605627</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,69 +3041,69 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Burlington, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Senior Data Architect (Hands on)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Azure and Databricks)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Git</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technical Architect, Integration Development</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sdq</t>
+          <t>eSentire</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Data &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>ProFocus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tra'Bian Enterprises</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0edabd1040dd11</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+          <t>Technical Architect, Integration Development</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Advanced Software Architect (Remote - United States)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Glue, EMR, Lambda, RDS, Azure, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e39da103dc0a30b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Branchburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>sdq</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,262 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Solutions Architect 4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Edgewater Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer, Fuel Performance &amp; Decarbonization</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b01aaa96bfc055c</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bitus Labs LLC</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329cce0cc21f01c1</t>
         </is>
       </c>
     </row>
